--- a/output/full_scan/batch_seq0_2026-05-29.xlsx
+++ b/output/full_scan/batch_seq0_2026-05-29.xlsx
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>3.92263321392685</v>
+        <v>3.922633213926849</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq0_2026-05-29.xlsx
+++ b/output/full_scan/batch_seq0_2026-05-29.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>2412</v>
+        <v>1303</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1472.09631262475</v>
+        <v>1700.162945001035</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>137</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>50.80501565006286</v>
+        <v>62.6184830527754</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>29.3214453809615</v>
+        <v>18.40213142434184</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.861004671860812</v>
+        <v>1.944720412417798</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.1823012141978369</v>
+        <v>0.9116141762497454</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>2408</v>
+        <v>2492</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1469.231371185974</v>
+        <v>1632.377817399118</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.53474841692946</v>
+        <v>91.76875381798716</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>19.37389734491432</v>
+        <v>51.14442003210835</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.893741982151541</v>
+        <v>0.2367722140974241</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.05038469501212</v>
+        <v>17.97390621876127</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>2434</v>
+        <v>2481</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>統懋</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1408.528675722459</v>
+        <v>1495.827346311015</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39.75</v>
+        <v>162.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>85.11554294265177</v>
+        <v>82.54759758353043</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25.44967407235439</v>
+        <v>51.59398641667129</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.619297912158606</v>
+        <v>0.8345692927216417</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.8125904166668301</v>
+        <v>3.327819917303222</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>2405</v>
+        <v>1447</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>輔信</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1361.208054202341</v>
+        <v>1474.709992865246</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.65</v>
+        <v>6.21</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>68.96605657522227</v>
+        <v>70.75240615530331</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>22.28738809987922</v>
+        <v>33.65457202110854</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4.81093198975233</v>
+        <v>1.839060031895764</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2111928220190644</v>
+        <v>0.0566647411179822</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2455</v>
+        <v>2412</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1348.543935133686</v>
+        <v>1472.09631262475</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>422</v>
+        <v>137</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.12338967237981</v>
+        <v>50.80501565006286</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>42.9925970319747</v>
+        <v>29.3214453809615</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2092399929472754</v>
+        <v>1.861004671860812</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0755226036177632</v>
+        <v>-0.1823012141978369</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>2399</v>
+        <v>2408</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>映泰</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1338.687497382295</v>
+        <v>1469.231371185974</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>47.9</v>
+        <v>347</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.99772563268836</v>
+        <v>66.53474841692946</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>42.68515852789145</v>
+        <v>19.37389734491432</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3937410917838133</v>
+        <v>0.893741982151541</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.09255202383066399</v>
+        <v>2.05038469501212</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>2419</v>
+        <v>1326</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>仲琦</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1307.902375291029</v>
+        <v>1451.785215621836</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>32.65</v>
+        <v>49.9</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.6467585711231</v>
+        <v>60.51617742223356</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>15.33014484819347</v>
+        <v>22.19804356882784</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.008462510752868</v>
+        <v>3.087240641256996</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3219436842091838</v>
+        <v>0.1814150498812607</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>2472</v>
+        <v>2495</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1284.349956414226</v>
+        <v>1448.335574587729</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>371</v>
+        <v>51.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>88.36618211792779</v>
+        <v>69.34352378198736</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>61.9065514497284</v>
+        <v>27.39252734930876</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.558627674701035</v>
+        <v>2.026238960916777</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>12.70351116208921</v>
+        <v>1.369194658759936</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>2438</v>
+        <v>2434</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>翔耀</t>
+          <t>統懋</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1275.727925120457</v>
+        <v>1408.528675722459</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>28.2</v>
+        <v>39.75</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>78.92352402080195</v>
+        <v>85.11554294265177</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24.66264149547861</v>
+        <v>25.44967407235439</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.871864491797997</v>
+        <v>6.619297912158606</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.6952204854748189</v>
+        <v>0.8125904166668301</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>2428</v>
+        <v>1409</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1253.634222440735</v>
+        <v>1364.177789284816</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>292</v>
+        <v>22.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>90.7122777106382</v>
+        <v>86.52582613095281</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>40.51427664469673</v>
+        <v>40.11018762781413</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.854275413683709</v>
+        <v>1.234464159693819</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>7.830746239060218</v>
+        <v>0.5226921399450184</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2464</v>
+        <v>2405</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>盟立</t>
+          <t>輔信</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1250.505874949072</v>
+        <v>1361.208054202341</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>184.5</v>
+        <v>17.65</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>76.78759391843613</v>
+        <v>68.96605657522227</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>52.4971764312976</v>
+        <v>22.28738809987922</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.571887799259416</v>
+        <v>4.81093198975233</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>4.360910941007766</v>
+        <v>0.2111928220190644</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2409</v>
+        <v>2478</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1244.613108468493</v>
+        <v>1356.347286156275</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.07571518492475</v>
+        <v>84.4212129620866</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.39209631049686</v>
+        <v>48.3164378847721</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.345258802921206</v>
+        <v>0.4846419903185625</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.236018994272539</v>
+        <v>3.899652026399409</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>2441</v>
+        <v>1256</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1232.986446878224</v>
+        <v>1355.718175950102</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>141.5</v>
+        <v>205.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>83.543876815516</v>
+        <v>71.30042078626551</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>39.41732921217682</v>
+        <v>37.84381212640091</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.846412620069611</v>
+        <v>2.172044248108204</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>4.308218845154421</v>
+        <v>1.388788898161873</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>2458</v>
+        <v>2455</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1225.124136985799</v>
+        <v>1348.543935133686</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>65.19707994768049</v>
+        <v>61.12338967237981</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.30553808807186</v>
+        <v>42.9925970319747</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5653778372547417</v>
+        <v>0.2092399929472754</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.009321443457186</v>
+        <v>0.0755226036177632</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>2426</v>
+        <v>2399</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>鼎元</t>
+          <t>映泰</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1203.675160926294</v>
+        <v>1338.687497382295</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>81.2</v>
+        <v>47.9</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>67.59438059181672</v>
+        <v>59.99772563268836</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>36.77243423787544</v>
+        <v>42.68515852789145</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.514175231708431</v>
+        <v>0.3937410917838133</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.300078124581872</v>
+        <v>-0.09255202383066399</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>2454</v>
+        <v>2419</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>仲琦</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1141.676686906586</v>
+        <v>1307.902375291029</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4310</v>
+        <v>32.65</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.45496454056421</v>
+        <v>56.6467585711231</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>57.42769417195601</v>
+        <v>15.33014484819347</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.842614112136633</v>
+        <v>2.008462510752868</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>51.53988129901836</v>
+        <v>0.3219436842091838</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>2397</v>
+        <v>2472</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>友通</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1138.232424176791</v>
+        <v>1284.349956414226</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>63.5</v>
+        <v>371</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>61.19943161113221</v>
+        <v>88.36618211792779</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.83271849240549</v>
+        <v>61.9065514497284</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6980456817820411</v>
+        <v>1.558627674701035</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.2898105571131206</v>
+        <v>12.70351116208921</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>2395</v>
+        <v>1339</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1121.463459298167</v>
+        <v>1278.203159681832</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>495</v>
+        <v>45.6</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>69.07072575762014</v>
+        <v>73.02768086184383</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>43.65314260905757</v>
+        <v>25.5076020170407</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.810178614260746</v>
+        <v>5.649142510029948</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0218591668871219</v>
+        <v>0.5148188008744335</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>2453</v>
+        <v>2438</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>凌群</t>
+          <t>翔耀</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1119.138788956397</v>
+        <v>1275.727925120457</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>61</v>
+        <v>28.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>67.03978617766444</v>
+        <v>78.92352402080195</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>39.62836035235547</v>
+        <v>24.66264149547861</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8702251435504648</v>
+        <v>3.871864491797997</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.6889109151789108</v>
+        <v>0.6952204854748189</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>2420</v>
+        <v>1444</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>新巨</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1118.595964278273</v>
+        <v>1257.421547772706</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>64.3</v>
+        <v>6.25</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>71.15126992127678</v>
+        <v>59.99999653030471</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>52.18722245740858</v>
+        <v>27.89214347026759</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9692087164902108</v>
+        <v>2.532256697053578</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.4813430495544799</v>
+        <v>0.033866780801538</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>2392</v>
+        <v>2428</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>正崴</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1117.066875345699</v>
+        <v>1253.634222440735</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>39.25</v>
+        <v>292</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.00898219246329</v>
+        <v>90.7122777106382</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13.4413796045245</v>
+        <v>40.51427664469673</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.630693014372087</v>
+        <v>2.854275413683709</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.6717163271515869</v>
+        <v>7.830746239060218</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2425</v>
+        <v>2464</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>承啟</t>
+          <t>盟立</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1113.447041377858</v>
+        <v>1250.505874949072</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>35.6</v>
+        <v>184.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.36250518660723</v>
+        <v>76.78759391843613</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30.52182267226522</v>
+        <v>52.4971764312976</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6166738238049269</v>
+        <v>0.571887799259416</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>1</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0800000567577614</v>
+        <v>4.360910941007766</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>2449</v>
+        <v>2409</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1113.251642792125</v>
+        <v>1244.613108468493</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>328.5</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.84721979373493</v>
+        <v>63.07571518492475</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>18.78667974073129</v>
+        <v>28.39209631049686</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.432041279648339</v>
+        <v>1.345258802921206</v>
       </c>
       <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.477823951349318</v>
+        <v>0.236018994272539</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>2451</v>
+        <v>1465</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1102.982812597544</v>
+        <v>1239.326004369413</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>338</v>
+        <v>12.45</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.9417955411792</v>
+        <v>60.05435519829355</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.5798087275466</v>
+        <v>18.49196503122114</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7445134371673622</v>
+        <v>2.334971673832325</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>2</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.464330145733886</v>
+        <v>0.0448243730298104</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>2406</v>
+        <v>1319</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>國碩</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1102.368520561024</v>
+        <v>1236.016153113402</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>34.55</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>56.20647080246784</v>
+        <v>76.75078872348314</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.55106019347688</v>
+        <v>23.88180834548431</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7833742204572088</v>
+        <v>3.142540659567913</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2853285354214959</v>
+        <v>1.397929228805805</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>2388</v>
+        <v>2441</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>威盛</t>
+          <t>超豐</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1096.067007817738</v>
+        <v>1232.986446878224</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>141.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.30433012726977</v>
+        <v>83.543876815516</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.35893310332771</v>
+        <v>39.41732921217682</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3156890552866456</v>
+        <v>0.846412620069611</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.092704493265797</v>
+        <v>4.308218845154421</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>2404</v>
+        <v>2498</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1095.151895160947</v>
+        <v>1231.90792199682</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1155</v>
+        <v>45.25</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>60.52094873880753</v>
+        <v>58.74158753887026</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>34.43294909638393</v>
+        <v>24.02573438027373</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6554125539382697</v>
+        <v>0.6195815367228068</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>12.88008044104687</v>
+        <v>0.0786826138784491</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>2401</v>
+        <v>1203</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1093.729108475014</v>
+        <v>1231.218403577429</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>30</v>
+        <v>43.55</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>67.10853059711035</v>
+        <v>59.64054781386917</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>35.38175587084584</v>
+        <v>21.90652960508984</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6621556469232296</v>
+        <v>0.7917006498802579</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3213646482409047</v>
+        <v>0.0246155421866725</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>2465</v>
+        <v>1785</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>麗臺</t>
+          <t>光洋科</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1093.25142950445</v>
+        <v>1229.642505394688</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>82.8</v>
+        <v>158.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.88396190796183</v>
+        <v>57.65733802461205</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>36.76435282431352</v>
+        <v>17.88831162118029</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5931103652045506</v>
+        <v>1.751992880388376</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.5781441805281595</v>
+        <v>-1.734709751748246</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>2450</v>
+        <v>2458</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>神腦</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1089.405824773673</v>
+        <v>1225.124136985799</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>29.85</v>
+        <v>162</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.82996838061921</v>
+        <v>65.19707994768049</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15.82649639195686</v>
+        <v>30.30553808807186</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.718848045927604</v>
+        <v>0.5653778372547417</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0264848447688763</v>
+        <v>1.009321443457186</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>2385</v>
+        <v>2426</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>鼎元</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1085.114573103348</v>
+        <v>1203.675160926294</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>135.5</v>
+        <v>81.2</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>60.37297343894498</v>
+        <v>67.59438059181672</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19.77570001998162</v>
+        <v>36.77243423787544</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8132227463128926</v>
+        <v>1.514175231708431</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4711826306615054</v>
+        <v>0.300078124581872</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>2474</v>
+        <v>2454</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1060.035665414867</v>
+        <v>1141.676686906586</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>203.5</v>
+        <v>4310</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.66903181610358</v>
+        <v>69.45496454056421</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24.29173788933413</v>
+        <v>57.42769417195601</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6.304577366701937</v>
+        <v>1.842614112136633</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.8464253704328848</v>
+        <v>51.53988129901836</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>2423</v>
+        <v>2397</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>固緯</t>
+          <t>友通</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1037.426177305845</v>
+        <v>1138.232424176791</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>82.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>70.27898980820829</v>
+        <v>61.19943161113221</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>54.75196413204521</v>
+        <v>24.83271849240549</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.8603100814617272</v>
+        <v>0.6980456817820411</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7783111606811435</v>
+        <v>0.2898105571131206</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>2440</v>
+        <v>2484</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>太空梭</t>
+          <t>希華</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1005.912391539102</v>
+        <v>1125.75436520953</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>17.6</v>
+        <v>54.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.50397336992195</v>
+        <v>66.6684467465108</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27.19376106465912</v>
+        <v>38.732613930411</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.677603217148505</v>
+        <v>1.271494292432456</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.1180777306389959</v>
+        <v>1.183982396197788</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>2390</v>
+        <v>2395</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>云辰</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1001.987465455543</v>
+        <v>1121.463459298167</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>10.8</v>
+        <v>495</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>66.00165463150978</v>
+        <v>69.07072575762014</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>35.60657665594862</v>
+        <v>43.65314260905757</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.032927582158368</v>
+        <v>1.810178614260746</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1153570815166908</v>
+        <v>0.0218591668871219</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>2414</v>
+        <v>2453</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>精技</t>
+          <t>凌群</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1001.902341290368</v>
+        <v>1119.138788956397</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>50.8</v>
+        <v>61</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>66.78179373310937</v>
+        <v>67.03978617766444</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>40.73039682442293</v>
+        <v>39.62836035235547</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5811904817259125</v>
+        <v>0.8702251435504648</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0778760003090246</v>
+        <v>0.6889109151789108</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>2467</v>
+        <v>2420</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>新巨</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>979.8250053020156</v>
+        <v>1118.595964278273</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>619</v>
+        <v>64.3</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.86536416135489</v>
+        <v>71.15126992127678</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>28.00061924008642</v>
+        <v>52.18722245740858</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5006165868423965</v>
+        <v>0.9692087164902108</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.573091627769436</v>
+        <v>0.4813430495544799</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>2459</v>
+        <v>2392</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>敦吉</t>
+          <t>正崴</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>979.8195237244246</v>
+        <v>1117.066875345699</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>39.25</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.34497512393678</v>
+        <v>54.00898219246329</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>12.59918362244122</v>
+        <v>13.4413796045245</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.305551957680319</v>
+        <v>1.630693014372087</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0705748396656586</v>
+        <v>0.6717163271515869</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>2436</v>
+        <v>2480</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>偉詮電</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>974.9287377311956</v>
+        <v>1117.057664912608</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>77.2</v>
+        <v>148.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.36756695571599</v>
+        <v>56.57627030715355</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.38562803388302</v>
+        <v>26.52196124824363</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8893753089658286</v>
+        <v>1.203977946025506</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1064391050240884</v>
+        <v>-0.2686550213017877</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>2421</v>
+        <v>2493</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>揚博</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>963.1076275838146</v>
+        <v>1115.843054550528</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>59.76208366091503</v>
+        <v>65.37223278020831</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.16766820500325</v>
+        <v>25.63779034859218</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6459681440382072</v>
+        <v>0.9676807313119284</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>1</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.122434405684388</v>
+        <v>2.724199109818785</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>2417</v>
+        <v>2425</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>圓剛</t>
+          <t>承啟</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>890.9434037571044</v>
+        <v>1113.447041377858</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>49</v>
+        <v>35.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.67882011799936</v>
+        <v>61.36250518660723</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>31.60145285620822</v>
+        <v>30.52182267226522</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.390993980597153</v>
+        <v>0.6166738238049269</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.4797680283981096</v>
+        <v>0.0800000567577614</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>2461</v>
+        <v>2483</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光群雷</t>
+          <t>百容</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>884.1669327827236</v>
+        <v>1113.341727411928</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>16.25</v>
+        <v>25.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>47.23091065412385</v>
+        <v>62.38386245917174</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13.04951717302836</v>
+        <v>34.30137434743267</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.49376697113809</v>
+        <v>0.583892367611635</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0164083260835309</v>
+        <v>0.096755112673299</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>2402</v>
+        <v>2449</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>毅嘉</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>873.270016495652</v>
+        <v>1113.251642792125</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>328.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.34806412611024</v>
+        <v>57.84721979373493</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.73618022835539</v>
+        <v>18.78667974073129</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.205793835213174</v>
+        <v>1.432041279648339</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.019282341725009</v>
+        <v>2.477823951349318</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>2439</v>
+        <v>2451</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>871.9135969114718</v>
+        <v>1102.982812597544</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>91.8</v>
+        <v>338</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,49 +2831,49 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>63.48698162342355</v>
+        <v>63.9417955411792</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24.51290665253552</v>
+        <v>24.5798087275466</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9272109824356364</v>
+        <v>0.7445134371673622</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.7696404099663366</v>
+        <v>-1.464330145733886</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>2413</v>
+        <v>2406</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>環科</t>
+          <t>國碩</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>846.6145074624419</v>
+        <v>1102.368520561024</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>51.2</v>
+        <v>34.55</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.15691306454044</v>
+        <v>56.20647080246784</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17.67928080259161</v>
+        <v>16.55106019347688</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.035293040651482</v>
+        <v>0.7833742204572088</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>2</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.6159004477328626</v>
+        <v>0.2853285354214959</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>2387</v>
+        <v>1815</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>精元</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>783.1162153356092</v>
+        <v>1099.500340038549</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>41.1</v>
+        <v>106</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.74236430760431</v>
+        <v>49.02515939176713</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19.2199140187219</v>
+        <v>10.61413706069286</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.107448205274129</v>
+        <v>0.5655961891928766</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.2788313746362618</v>
+        <v>0.0253041539498832</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>2460</v>
+        <v>2388</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>建通</t>
+          <t>威盛</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>770.3655052786231</v>
+        <v>1096.067007817738</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>32.4</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.11457057666755</v>
+        <v>52.30433012726977</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12.62776010224395</v>
+        <v>31.35893310332771</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4033754144286496</v>
+        <v>0.3156890552866456</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2092363312334694</v>
+        <v>-1.092704493265797</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>2457</v>
+        <v>2404</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>飛宏</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>763.231882249994</v>
+        <v>1095.151895160947</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>26</v>
+        <v>1155</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.76346389075463</v>
+        <v>60.52094873880753</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>12.71570731711388</v>
+        <v>34.43294909638393</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.211471318632589</v>
+        <v>0.6554125539382697</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1421923526116692</v>
+        <v>12.88008044104687</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>2431</v>
+        <v>2401</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>聯昌</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>708.4308553668641</v>
+        <v>1093.729108475014</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>10.45</v>
+        <v>30</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>44.32199368868548</v>
+        <v>67.10853059711035</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24.1589467580946</v>
+        <v>35.38175587084584</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.198502235588992</v>
+        <v>0.6621556469232296</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0560921835865559</v>
+        <v>0.3213646482409047</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, williams_r_recovery</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>2393</v>
+        <v>2465</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>億光</t>
+          <t>麗臺</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>539.7729007153674</v>
+        <v>1093.25142950445</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>62.5</v>
+        <v>82.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>35.73892282192992</v>
+        <v>56.88396190796183</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>27.29569179445286</v>
+        <v>36.76435282431352</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7453492690212937</v>
+        <v>0.5931103652045506</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.5224574891209048</v>
+        <v>-0.5781441805281595</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>2430</v>
+        <v>2450</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>燦坤</t>
+          <t>神腦</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>498.1170512848139</v>
+        <v>1089.405824773673</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>18.3</v>
+        <v>29.85</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>29.67047991509285</v>
+        <v>58.82996838061921</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>61.66449253579052</v>
+        <v>15.82649639195686</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7287738223843301</v>
+        <v>2.718848045927604</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>1</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0465629829861611</v>
+        <v>0.0264848447688763</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>2427</v>
+        <v>2476</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>三商電</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>473.6774250798677</v>
+        <v>1087.028589596332</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>20.6</v>
+        <v>122</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>39.78625769282724</v>
+        <v>56.17426253847279</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>31.21732580606724</v>
+        <v>23.43287242410611</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.377837053605994</v>
+        <v>0.8604450366053737</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0565787144982381</v>
+        <v>-0.1459019139293698</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>2466</v>
+        <v>2385</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>冠西電</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>465.3619854193149</v>
+        <v>1085.114573103348</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>47.6</v>
+        <v>135.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>41.36054702976461</v>
+        <v>60.37297343894498</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.31724476901546</v>
+        <v>19.77570001998162</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.02477133656759</v>
+        <v>0.8132227463128926</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0251254019986517</v>
+        <v>0.4711826306615054</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>2429</v>
+        <v>2474</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>銘旺科</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>442.9445338192375</v>
+        <v>1060.035665414867</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>47.35</v>
+        <v>203.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.82967731991811</v>
+        <v>53.66903181610358</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.57760792162319</v>
+        <v>24.29173788933413</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5472487209379516</v>
+        <v>6.304577366701937</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>1</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.5704250481610831</v>
+        <v>0.8464253704328848</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>2442</v>
+        <v>2423</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>新美齊</t>
+          <t>固緯</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>442.7331894688156</v>
+        <v>1037.426177305845</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>18.65</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.72109420728157</v>
+        <v>70.27898980820829</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.7775848355078</v>
+        <v>54.75196413204521</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.597997329731682</v>
+        <v>0.8603100814617272</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.08164336779198431</v>
+        <v>0.7783111606811435</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>2462</v>
+        <v>2491</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>良得電</t>
+          <t>吉祥全</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>439.8505376161281</v>
+        <v>1029.427763157312</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>21</v>
+        <v>23.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.01251794135383</v>
+        <v>66.60825016448564</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>11.37507874842122</v>
+        <v>42.23090870212144</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8349099880988315</v>
+        <v>1.284016034084594</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1109059733144463</v>
+        <v>0.1297364364360165</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>2433</v>
+        <v>2477</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>互盛電</t>
+          <t>美隆電</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>337.2277863403833</v>
+        <v>1020.553925810225</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>43.4</v>
+        <v>21.55</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>28.09633876366757</v>
+        <v>51.53698076257715</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.94070583111196</v>
+        <v>19.26752659831407</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6484464708500556</v>
+        <v>1.523032573164831</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.180824449165559</v>
+        <v>0.1659049898609428</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>2424</v>
+        <v>1423</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>隴華</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>321.2423596237342</v>
+        <v>1017.691310272238</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>12.5</v>
+        <v>41.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>30.93817017842773</v>
+        <v>54.73186064507379</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.62580708376428</v>
+        <v>24.10479862425889</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5835293658625403</v>
+        <v>0.7954698457762543</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.616300370999928</v>
+        <v>0.044846456417672</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>2432</v>
+        <v>2440</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>倚天</t>
+          <t>太空梭</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>321.1597033696154</v>
+        <v>1005.912391539102</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>26.45</v>
+        <v>17.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.59409895316765</v>
+        <v>53.50397336992195</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.54736990562367</v>
+        <v>27.19376106465912</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6685608176906842</v>
+        <v>0.677603217148505</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.008357569756104299</v>
+        <v>-0.1180777306389959</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>2415</v>
+        <v>2390</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>錩新</t>
+          <t>云辰</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>316.4903464164941</v>
+        <v>1001.987465455543</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>27</v>
+        <v>10.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.43253966078477</v>
+        <v>66.00165463150978</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.0097744628882</v>
+        <v>35.60657665594862</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.723318262108629</v>
+        <v>1.032927582158368</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0713429785712161</v>
+        <v>0.1153570815166908</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>2444</v>
+        <v>2414</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>兆勁</t>
+          <t>精技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>316.1558055631178</v>
+        <v>1001.902341290368</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>12.4</v>
+        <v>50.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.56381330284056</v>
+        <v>66.78179373310937</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.76267406658117</v>
+        <v>40.73039682442293</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.120459555633669</v>
+        <v>0.5811904817259125</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0913419226863581</v>
+        <v>0.0778760003090246</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>2471</v>
+        <v>1309</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>資通</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>215.0211665247273</v>
+        <v>989.5068734253376</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>51.1</v>
+        <v>15.7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.20058356786348</v>
+        <v>42.2241174825646</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.52926573980116</v>
+        <v>15.29713062343536</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7138961447864866</v>
+        <v>1.536238259418238</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,62 +3803,6316 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0592217478132304</v>
+        <v>0.0334911607178929</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
+        <v>2467</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>志聖</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>979.8250053020156</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>55.86536416135489</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>28.00061924008642</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.5006165868423965</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>-1.573091627769436</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>2459</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>979.8195237244246</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>55.34497512393678</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>12.59918362244122</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>1.305551957680319</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>0.0705748396656586</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>2436</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>偉詮電</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>974.9287377311956</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>57.36756695571599</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>22.38562803388302</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.8893753089658286</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0.1064391050240884</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>968.8440785379464</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>46.42198511349656</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>17.50035969569003</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>9.834168901475056</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>-0.1513643938246726</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>2421</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>963.1076275838146</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>59.76208366091503</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>17.16766820500325</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.6459681440382072</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1.122434405684388</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>勤益控</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>948.4257912769332</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>35.12450660434547</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>39.06623234983823</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>4.054561559489738</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>0.0585436536481396</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>1435</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>中福</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>943.4299318254082</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>49.81911581211848</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>7.899471079306138</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>8.481734204897169</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0.1142738661580247</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>大魯閣</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>930.6062651686716</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>54.72982165087004</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>23.74837181864626</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>2.556541325037704</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>0.0423654109200001</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, williams_r_recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>910.9518026652224</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>48.649818155984</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>20.02580132626555</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>2.134160039419629</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>-0.3041922619753113</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>泰山</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>900.9401891725756</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>50.80732998008207</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>22.19851611048318</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1.404065950742149</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>0.0040076579368</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, williams_r_recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>2417</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>圓剛</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>890.9434037571044</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>53.67882011799936</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>31.60145285620822</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.390993980597153</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>-0.4797680283981096</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>2461</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>光群雷</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>884.1669327827236</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>47.23091065412385</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>13.04951717302836</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>1.49376697113809</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0.0164083260835309</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>2488</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>漢平</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>876.5531485145686</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>59.35030560713826</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>23.45825846841466</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.6319775403326741</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0.0165538141564518</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>1301</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>874.9768759393357</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>50.93898689747733</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>23.6625900951582</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>2.228758686595874</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>-0.0059226108115166</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, williams_r_recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>2402</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>毅嘉</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>873.270016495652</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>55.34806412611024</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>16.73618022835539</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1.205793835213174</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>-0.019282341725009</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>2486</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>一詮</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>872.354989454112</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>53.86293291646399</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>27.18769103487668</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.8401001879294958</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-3.888908610094969</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>2439</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>美律</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>871.9135969114718</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>63.48698162342355</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>24.51290665253552</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.9272109824356364</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.7696404099663366</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>2489</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>瑞軒</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>853.379755467834</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>57.7960459183838</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>20.84086987166444</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.7070563125464104</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0.5462726396286581</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>2485</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>兆赫</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>848.4801099902384</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>56.05744765741432</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>21.39026560030783</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.6281188248311967</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>0.4482561186442098</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>2413</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>環科</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>846.6145074624419</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>58.15691306454044</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>17.67928080259161</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>1.035293040651482</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.6159004477328626</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>遠東新</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>820.3512915769168</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>46.74786690961339</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>22.47922116943848</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>6.870724988229808</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-0.156329914018831</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>1455</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>集盛</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>807.0992590790952</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>61.73878499672067</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>23.47215306718588</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1.40767285711845</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.07400147462169029</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>三洋實業</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>802.8647680981521</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>51.50256804940685</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>20.92224743887874</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>2.721904091621613</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>1.458335478040027</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>2387</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>精元</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>783.1162153356092</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>56.74236430760431</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>19.2199140187219</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>1.107448205274129</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.2788313746362618</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>廣華-KY</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>773.005947253038</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>55.40895808401457</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>14.6835327324258</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>2.100301986294004</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.0547647500760279</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>2460</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>建通</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>770.3655052786231</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>49.11457057666755</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>12.62776010224395</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.4033754144286496</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-0.2092363312334694</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>1595</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>川寶</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>769.3966739457447</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>52.73909865934202</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>46.60447343542766</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.6471416682384639</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-2.085085443860004</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>1470</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>大統新創</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>766.6579580567818</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>52.73900936455041</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>4.615822648083783</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.0604587610790679</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>0.06435387567387529</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, cci_momentum, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>2457</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>飛宏</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>763.231882249994</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>54.76346389075463</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>12.71570731711388</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1.211471318632589</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>0.1421923526116692</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>1323</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>永裕</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>762.5770038767041</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>50.19342937448928</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>9.743564258516026</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.3668619093007919</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>0.0896936991502421</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>2431</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>聯昌</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>708.4308553668641</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>44.32199368868548</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>24.1589467580946</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.198502235588992</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>0.0560921835865559</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, williams_r_recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>1312</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>國喬</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>708.0794427998528</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>50.08310505258979</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>29.84364630858362</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>3.493636058147362</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0.1063474662120607</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>東泥</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>701.2371769736178</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>50.31471794048992</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>21.24069913102856</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1.301475590895831</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>0.0193216392419793</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>1336</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>台翰</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>697.3159443164657</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>41.14883683009327</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>23.4462355175367</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.8559850105809964</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>0.0123111164130482</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>東華</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>689.9776839375585</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>51.85131458263721</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>12.52520256325904</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>1.406230873644324</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.0237163187311417</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>1466</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>聚隆</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>688.6322442580391</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>32.2882511886792</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>24.18341281498998</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>2.536875668058087</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-0.0515037471158412</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>1434</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>福懋</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>684.4050265581764</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>46.76087327094967</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>29.8204395012716</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1.877502968961936</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.0202062936156153</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>宏洲</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>683.7890709764744</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>49.39859664547018</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>7.636023096876367</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>1.783748425463028</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.0091638416855589</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>立益</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>678.9584490147379</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>50.32280518143605</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>12.65967128064177</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.5773803952210995</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.2038798396368436</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>南紡</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>677.409724210587</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>57.73940524362701</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>27.22616968958596</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>2.044604677115121</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>0.1113943747466204</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>1419</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>新紡</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>662.9868790660914</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>51.14298226199973</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>13.71539651332594</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.7550751484454393</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>0.0633556954040479</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>1341</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>富林-KY</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>658.0428150569691</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>47.61170241836129</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>16.12912286870738</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.356453234823657</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-0.0778909778503652</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>643.4249704485503</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>50.782778924934</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>11.83306373687582</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1.618227290848613</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-0.0467507342573538</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>1416</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>廣豐</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>606.0686030840006</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>37.95249989937048</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>37.80374214862864</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.9548470903465436</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>0.0034636119061891</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>1321</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>大洋</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>590.1229968668358</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>26.28323241120609</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>52.35131475317461</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>1.531043910125786</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>0.0612790878462998</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>環泥</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>589.4421290710637</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>34.82365388665859</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>45.99954507453175</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.964073987788538</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.0076961133512535</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>愛之味</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>586.0542775743078</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>50.46523600374482</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>37.12162781482222</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.6583115858509174</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.0478937418057059</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>得力</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>581.3942336351836</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>52.13605987914113</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>13.64419518247834</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.7595118917624144</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.0241075875881225</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>1313</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>聯成</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>569.3796929353661</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>43.99536480307152</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>18.69874842810637</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>1.104664041400441</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>0.0397213658482407</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>聯華食</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>568.940284066118</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>42.87342041857864</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>19.43567217739536</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>1.068944171319293</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0.0172045992147948</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>1340</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>勝悅-KY</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>567.8872070488404</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>40.57535356357305</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>26.97050583938585</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.6201421968678136</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0.0386528001125309</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>1236</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>宏亞</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>567.4127426619038</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>41.98352908929837</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>22.22668262391305</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.4354572846144044</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>0.0431118639750661</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>雋揚</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>561.0787399155558</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>50.02442843646596</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>4.190837937508959</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.8881382611167911</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.1043236333199346</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>台聚</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>550.2409921945283</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>40.0928050988648</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>28.99424679045516</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>1.289493300897433</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.0377295289371171</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>2393</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>億光</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>539.7729007153674</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>35.73892282192992</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>27.29569179445286</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.7453492690212937</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.5224574891209048</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>華夏</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>535.867739518114</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>39.92040988713914</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>17.65009101497932</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.9859279590857876</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>0.0447792023920217</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>532.8515975163237</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>25.45403105285891</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>24.70841451558421</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>1.156577506297201</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>-1.325424648619868</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>佳和</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>522.6805909383073</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>49.69087918833294</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>11.94211032356586</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>1.538788933857324</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.0377055346082302</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>幸福</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>508.0898138212916</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>32.7728900831367</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>60.02881358445704</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.7789168641543713</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>-0.0144712390342653</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>2430</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>燦坤</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>498.1170512848139</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>29.67047991509285</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>61.66449253579052</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.7287738223843301</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.0465629829861611</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>味全</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>490.9449999663282</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>39.28910715800787</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>54.91711198067085</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.6448129701141097</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.0454674191787815</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>1337</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>再生-KY</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>486.3828095250478</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>41.23140252734417</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>34.79816251640134</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>1.200315981679969</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.0246790893121051</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>1452</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>宏益</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>477.2615618431115</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>28.50134375330643</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>34.38635989383889</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.5125475763715087</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0303817061007242</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>嘉裕</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>473.731238241224</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>28.70937345905287</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>31.50230496764938</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>1.306411274839449</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.0128571093692154</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>2427</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>三商電</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>473.6774250798677</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>39.78625769282724</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>31.21732580606724</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>1.377837053605994</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.0565787144982381</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>470.2831891390874</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>33.6439965436233</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>28.72033948836825</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>1.415549836982719</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-0.0219294614653182</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>三地開發</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>468.1353604889317</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>29.24256143614772</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>39.93796454788722</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.1931126140501974</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>0.2225314587739923</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>大東</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>465.3672630842748</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>38.80976082114753</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>14.41792782634113</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.7212780257378772</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>-0.0243113614126294</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>2466</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>冠西電</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>465.3619854193149</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>41.36054702976461</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>21.31724476901546</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>1.02477133656759</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>-0.0251254019986517</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>台富</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>464.9742106146733</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>40.58519887399138</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>20.30504467544933</v>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>0.5901170810869184</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>-0.0881673521848763</v>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>南緯</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>463.880510317234</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>37.71254899354616</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>12.45394072732793</v>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>0.7981173525157583</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>-0.0144958162358765</v>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>1235</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>興泰</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>460.6953416735449</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>50.59259128915033</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>15.49843972670576</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>0.8861286115270446</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>0.0094469773130396</v>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>1229</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>聯華</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>452.9145925711542</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>43.9811120147663</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>31.38353575951408</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>0.9265461092661632</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>0.1767652004052602</v>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>1233</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>天仁</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>452.654632275352</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>33.47448210086642</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>19.34472594275725</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>14.19228635851924</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>-0.0434626701373983</v>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>大飲</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>449.5227557091134</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>46.23148544142904</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>10.34423892593104</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>0.6902716328840416</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>-0.0317166550177913</v>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>1315</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>達新</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>446.214072265799</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>48.08305507488555</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>14.76653711517426</v>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>1.113328933808829</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>0.1564678505852914</v>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>嘉泥</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>445.6628190655225</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>55.95255860040886</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>21.38089782853357</v>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>1.244534498661788</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>0.0455756500995813</v>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>1325</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>恆大</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>444.4006255789711</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>50.47853298080126</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>17.60650538627015</v>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>0.612554026902455</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>0.0200125807025166</v>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>2429</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>銘旺科</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>442.9445338192375</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>45.82967731991811</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>15.57760792162319</v>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>0.5472487209379516</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>-0.5704250481610831</v>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>2442</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>新美齊</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>442.7331894688156</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>48.72109420728157</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>16.7775848355078</v>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>1.597997329731682</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>0.08164336779198431</v>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>442.392438166397</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>45.00225931084088</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>14.28352557490386</v>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.7963699909450253</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>0.0319144032222444</v>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>2462</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>良得電</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>439.8505376161281</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>50.01251794135383</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>11.37507874842122</v>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>0.8349099880988315</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>0.1109059733144463</v>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>1451</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>年興</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>439.6937405660327</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>39.11303124968043</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>16.68615679371202</v>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>0.4740966839954936</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>0.0070063910814654</v>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>亞聚</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>435.4944288077409</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>39.67361551780223</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>18.15527403490973</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.9678093646147274</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>0.0701875384496819</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>福懋油</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>434.9177541919144</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>39.1540345119323</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>18.06302030761758</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>0.3369030506824633</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>-0.0549245696851272</v>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>八貫</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>431.8655518950432</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>45.4649674796627</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>13.01464340144408</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>0.7446172894109052</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>-0.3638809003727865</v>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>中石化</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>428.9655807859033</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>47.17778642018053</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>5.749707357428952</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.96160246547066</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>0.0298482145396536</v>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>1232</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>大統益</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>427.1463754848389</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>43.97878550328781</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>10.88920211901996</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>1.209235284063881</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>-0.0008058935335385</v>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>1456</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>怡華</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>426.3428883073479</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>37.97809779559311</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>14.10816749998292</v>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.4237215457282089</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>-0.0461495273724466</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>1460</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>宏遠</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>420.0890080074083</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>46.1596237308145</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>17.40052772500616</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>0.9096725659800764</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>-0.0177003158997973</v>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>信大</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>362.6662054008656</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>35.2187979214975</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>48.53057206847483</v>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>0.4627170195526715</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>-0.0369092108220167</v>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>福壽</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>361.9576032778419</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>38.0289580059986</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>45.50656061745936</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>0.5679796432391168</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>-0.0007065317598724</v>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>1436</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>華友聯</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>361.5401380433834</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>17.95155997051576</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>49.98322700025288</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>0.5032354544353069</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>-0.0938485875393873</v>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>1310</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>台苯</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>358.8941442195356</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>37.5201644627228</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>37.30266226806434</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>1.167478172704304</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>0.0556023725092533</v>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>宜進</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>352.4259705600273</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>34.75988266946207</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>18.00517496688086</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>1.061184695408729</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>0.0127857867836348</v>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>1414</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>東和</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>351.5151076836033</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>30.80152926142117</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>41.01293694562875</v>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>0.74862175267103</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>-0.1114674155052044</v>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>大將</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>348.947998800247</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>32.00765330505722</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>17.26846851752183</v>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>0.9276824294989976</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>0.0119210283352986</v>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>台榮</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>347.2160876150205</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>22.04194094291229</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>30.82871848770535</v>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>0.8910312315215072</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>-0.0269774036759265</v>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>大宇</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>346.1760600681696</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>40.11192297081407</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>11.16737992726406</v>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>1.253877486996278</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>0.0056323549718946</v>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>1459</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>聯發</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>345.9401302808458</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>43.53340136199645</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>16.28918936151144</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>0.6337184223941452</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>-0.0279764219054289</v>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>1468</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>昶和</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>345.9282369574064</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>46.23855800790736</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>10.39690796381477</v>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>1.13665084684115</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>-0.0107717204658999</v>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>1446</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>宏和</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>344.6326710277655</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>51.64693176474784</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>22.41067638030871</v>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>1.242023144711737</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>0.0863762141267387</v>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>1234</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>黑松</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>343.8709635060907</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>46.47800673066934</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>24.8576332458299</v>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>0.7314977693351844</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>0.0816923693355369</v>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>上曜</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>337.5042624988408</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>31.24721016938632</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>23.5406258421087</v>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>0.7683431516167381</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N167" s="2" t="n">
+        <v>-0.0319013147098599</v>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>2433</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>互盛電</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>337.2277863403833</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>28.09633876366757</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>23.94070583111196</v>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>0.6484464708500556</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>-0.180824449165559</v>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>1442</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>名軒</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>332.8072108123656</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>38.81328434124711</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>13.22709316813427</v>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>0.6761450965204964</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N169" s="2" t="n">
+        <v>-0.06777836375796351</v>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>南染</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>331.6695934736846</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>37.41009871344202</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>14.90229237708989</v>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>0.2791159816697614</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N170" s="2" t="n">
+        <v>0.0942644009159212</v>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>2424</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>隴華</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>321.2423596237342</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>30.93817017842773</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>20.62580708376428</v>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>0.5835293658625403</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>-0.616300370999928</v>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>2432</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>倚天</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>321.1597033696154</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>26.45</v>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>45.59409895316765</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>19.54736990562367</v>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>0.6685608176906842</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N172" s="2" t="n">
+        <v>-0.008357569756104299</v>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>大成</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>320.2626455728803</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H173" s="2" t="n">
+        <v>48.49884219788224</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>13.46333786683406</v>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>1.225280779155312</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N173" s="2" t="n">
+        <v>-0.024543452257881</v>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>2415</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>錩新</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>316.4903464164941</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>47.43253966078477</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>16.0097744628882</v>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>0.723318262108629</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N174" s="2" t="n">
+        <v>0.0713429785712161</v>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>2444</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>兆勁</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>316.1558055631178</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H175" s="2" t="n">
+        <v>40.56381330284056</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>12.76267406658117</v>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>1.120459555633669</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N175" s="2" t="n">
+        <v>-0.0913419226863581</v>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>濱川</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>307.6122169995596</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H176" s="2" t="n">
+        <v>41.45063546989374</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>14.07934825335476</v>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>0.2404101351954534</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N176" s="2" t="n">
+        <v>-0.313605462805841</v>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>樂事綠能</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>238.5831740325761</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H177" s="2" t="n">
+        <v>51.59309211442791</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>16.0487483451497</v>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>0.7893414686055772</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N177" s="2" t="n">
+        <v>0.2398179253197201</v>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>強盛新</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>215.8527991450622</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>43.74255430426109</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>10.15955891614356</v>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>1.236640853055415</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>-0.045449425944314</v>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>2482</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>連宇</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>215.2668375721454</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H179" s="2" t="n">
+        <v>41.54515982888253</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>12.11753170649868</v>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>1.283063918662037</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N179" s="2" t="n">
+        <v>-0.0008475629348957</v>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>2471</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>資通</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>215.0211665247273</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H180" s="2" t="n">
+        <v>49.20058356786348</v>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>12.52926573980116</v>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>0.7138961447864866</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N180" s="2" t="n">
+        <v>0.0592217478132304</v>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>三芳</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>214.0331334797804</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H181" s="2" t="n">
+        <v>44.45022339134812</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>12.47559830876591</v>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>0.8503825756945484</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N181" s="2" t="n">
+        <v>-0.0578668564064469</v>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
         <v>2468</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>華經</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D64" s="2" t="n">
+      <c r="C182" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D182" s="2" t="n">
         <v>207.7369771793293</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E182" s="2" t="n">
         <v>33.2</v>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64" s="2" t="n">
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H182" s="2" t="n">
         <v>45.52875099000672</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="I182" s="2" t="n">
         <v>9.466706878046327</v>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="J182" s="2" t="n">
         <v>0.7029426384289925</v>
       </c>
-      <c r="K64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N64" s="2" t="n">
+      <c r="K182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N182" s="2" t="n">
         <v>0.0607967127402601</v>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="O182" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
